--- a/artfynd/A 42233-2022 artfynd.xlsx
+++ b/artfynd/A 42233-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42233-2022 artfynd.xlsx
+++ b/artfynd/A 42233-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114028491</v>
+        <v>114029578</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>799787</v>
+        <v>799784</v>
       </c>
       <c r="R2" t="n">
-        <v>7331381</v>
+        <v>7331341</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114029578</v>
+        <v>114028491</v>
       </c>
       <c r="B3" t="n">
-        <v>56720</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>799784</v>
+        <v>799787</v>
       </c>
       <c r="R3" t="n">
-        <v>7331341</v>
+        <v>7331381</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>

--- a/artfynd/A 42233-2022 artfynd.xlsx
+++ b/artfynd/A 42233-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114029578</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114028491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>